--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87376</v>
+        <v>87382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87586</v>
+        <v>87592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90799</v>
+        <v>90805</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87382</v>
+        <v>87386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87592</v>
+        <v>87596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90805</v>
+        <v>90809</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87596</v>
+        <v>87598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90809</v>
+        <v>90811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87598</v>
+        <v>87611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90811</v>
+        <v>90824</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90824</v>
+        <v>90826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90826</v>
+        <v>90829</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90829</v>
+        <v>90839</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90839</v>
+        <v>90840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90840</v>
+        <v>90843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90843</v>
+        <v>90848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90848</v>
+        <v>90859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90859</v>
+        <v>90860</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90860</v>
+        <v>90863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 9518-2026 artfynd.xlsx
+++ b/artfynd/A 9518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106636</v>
       </c>
       <c r="B2" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105301</v>
       </c>
       <c r="B3" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137105313</v>
       </c>
       <c r="B4" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105314</v>
       </c>
       <c r="B5" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137105299</v>
       </c>
       <c r="B6" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137105302</v>
       </c>
       <c r="B7" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137105309</v>
       </c>
       <c r="B8" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137106635</v>
       </c>
       <c r="B9" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137105300</v>
       </c>
       <c r="B10" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137105310</v>
       </c>
       <c r="B11" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137105303</v>
       </c>
       <c r="B12" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137105308</v>
       </c>
       <c r="B13" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137105311</v>
       </c>
       <c r="B14" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137105312</v>
       </c>
       <c r="B15" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137106634</v>
       </c>
       <c r="B16" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>137105304</v>
       </c>
       <c r="B17" t="n">
-        <v>90863</v>
+        <v>90867</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
